--- a/Hand_edited_log/1/StudentsSolution.xlsx
+++ b/Hand_edited_log/1/StudentsSolution.xlsx
@@ -49,10 +49,10 @@
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>06-12-2025 22:03:52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06-12-2025 22:04:30</x:t>
+    <x:t>06-12-2025 22:31:53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06-12-2025 22:33:39</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>

--- a/Hand_edited_log/1/StudentsSolution.xlsx
+++ b/Hand_edited_log/1/StudentsSolution.xlsx
@@ -49,10 +49,10 @@
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>06-12-2025 22:31:53</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06-12-2025 22:33:39</x:t>
+    <x:t>06-12-2025 22:43:17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06-12-2025 22:45:19</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>

--- a/Hand_edited_log/1/StudentsSolution.xlsx
+++ b/Hand_edited_log/1/StudentsSolution.xlsx
@@ -49,10 +49,10 @@
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>06-12-2025 22:43:17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06-12-2025 22:45:19</x:t>
+    <x:t>06-12-2025 23:14:17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06-12-2025 23:16:07</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>

--- a/Hand_edited_log/1/StudentsSolution.xlsx
+++ b/Hand_edited_log/1/StudentsSolution.xlsx
@@ -43,52 +43,58 @@
     <x:t>AnhDThe187386</x:t>
   </x:si>
   <x:si>
-    <x:t>Failed</x:t>
+    <x:t>Success</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 06:20:19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 06:22:32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>anlpvhe187047</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cuongnvhe181200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 06:22:15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungdvhe181404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungtdhe186461</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 06:22:22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duongnthe186310</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Not Run</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>06-12-2025 23:14:17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06-12-2025 23:16:07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>anlpvhe187047</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Not Run</x:t>
-  </x:si>
-  <x:si>
     <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cuongnvhe181200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dungdvhe181404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dungtdhe186461</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duongnthe186310</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>
@@ -201,7 +207,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FF90EE90"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -601,394 +607,394 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="A3" s="2" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" s="2" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="C3" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F3" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G3" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="2" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="B4" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D4" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E4" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="0" t="s">
+      <x:c r="F4" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G4" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+    </x:row>
+    <x:row r="5" spans="1:7">
+      <x:c r="A5" s="2" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
+      <x:c r="B5" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D5" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E5" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:7">
-      <x:c r="A5" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
+      <x:c r="F5" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G5" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:7">
+      <x:c r="A6" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
+      <x:c r="C6" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D6" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E6" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:7">
-      <x:c r="A6" s="0" t="s">
+      <x:c r="F6" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G6" s="2" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Hand_edited_log/1/StudentsSolution.xlsx
+++ b/Hand_edited_log/1/StudentsSolution.xlsx
@@ -49,10 +49,10 @@
     <x:t>5</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 06:20:19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 06:22:32</x:t>
+    <x:t>07-12-2025 12:59:03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 13:01:01</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -61,112 +61,163 @@
     <x:t>anlpvhe187047</x:t>
   </x:si>
   <x:si>
+    <x:t>07-12-2025 13:01:17</x:t>
+  </x:si>
+  <x:si>
     <x:t>3</x:t>
   </x:si>
   <x:si>
     <x:t>cuongnvhe181200</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 06:22:15</x:t>
+    <x:t>07-12-2025 13:01:07</x:t>
   </x:si>
   <x:si>
     <x:t>4</x:t>
   </x:si>
   <x:si>
+    <x:t>ducnthe180869</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Failed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 12:59:32</x:t>
+  </x:si>
+  <x:si>
     <x:t>dungdvhe181404</x:t>
   </x:si>
   <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
     <x:t>dungtdhe186461</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 06:22:22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
+    <x:t>7</x:t>
   </x:si>
   <x:si>
     <x:t>duongnthe186310</x:t>
   </x:si>
   <x:si>
+    <x:t>07-12-2025 13:01:40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DuyCNHE187327</x:t>
+  </x:si>
+  <x:si>
     <x:t>Not Run</x:t>
   </x:si>
   <x:si>
-    <x:t>0</x:t>
-  </x:si>
-  <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DuyCNHE187327</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
+    <x:t>9</x:t>
   </x:si>
   <x:si>
     <x:t>duyldhe176352</x:t>
   </x:si>
   <x:si>
-    <x:t>9</x:t>
+    <x:t>10</x:t>
   </x:si>
   <x:si>
     <x:t>duynthe180374</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GiangPTHE171781</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
   </x:si>
   <x:si>
     <x:t>hieunqhe171297</x:t>
   </x:si>
   <x:si>
-    <x:t>11</x:t>
+    <x:t>13</x:t>
   </x:si>
   <x:si>
     <x:t>HoangHHHE182296</x:t>
   </x:si>
   <x:si>
-    <x:t>12</x:t>
+    <x:t>14</x:t>
   </x:si>
   <x:si>
     <x:t>hungpvahe180492</x:t>
   </x:si>
   <x:si>
-    <x:t>13</x:t>
+    <x:t>15</x:t>
   </x:si>
   <x:si>
     <x:t>KienTTHE186727</x:t>
   </x:si>
   <x:si>
-    <x:t>14</x:t>
+    <x:t>16</x:t>
   </x:si>
   <x:si>
     <x:t>linhmndhe186854</x:t>
   </x:si>
   <x:si>
-    <x:t>15</x:t>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>linhndhe172819</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LongNBHE186897</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
   </x:si>
   <x:si>
     <x:t>manhcdhe176818</x:t>
   </x:si>
   <x:si>
-    <x:t>16</x:t>
+    <x:t>20</x:t>
   </x:si>
   <x:si>
     <x:t>MinhLAHE180101</x:t>
   </x:si>
   <x:si>
-    <x:t>17</x:t>
+    <x:t>21</x:t>
   </x:si>
   <x:si>
     <x:t>nguyendvhe176752</x:t>
   </x:si>
   <x:si>
-    <x:t>18</x:t>
+    <x:t>22</x:t>
   </x:si>
   <x:si>
     <x:t>nhandndhe180152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sonnvhhe182275</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tainhhe181471</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tungbdhe172875</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -193,7 +244,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -208,6 +259,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -230,7 +286,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -240,8 +296,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -251,6 +310,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -549,7 +612,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G19"/>
+  <x:dimension ref="A1:G26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="3.424911" style="0" customWidth="1"/>
@@ -626,15 +689,15 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
         <x:v>7</x:v>
@@ -649,30 +712,30 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G4" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
-      <x:c r="A5" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B5" s="2" t="s">
+      <x:c r="A5" s="3" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C5" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E5" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F5" s="2" t="s">
+      <x:c r="B5" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D5" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E5" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F5" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G5" s="2" t="s">
-        <x:v>12</x:v>
+      <x:c r="G5" s="3" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
@@ -680,7 +743,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
         <x:v>7</x:v>
@@ -695,306 +758,467 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G6" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
-      <x:c r="A7" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="A7" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B7" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E7" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F7" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G7" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:7">
+      <x:c r="A8" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B8" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E8" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F8" s="2" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:7">
-      <x:c r="A8" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>26</x:v>
+      <x:c r="G8" s="2" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:7">
+      <x:c r="A20" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:7">
+      <x:c r="A21" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:7">
+      <x:c r="A22" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:7">
+      <x:c r="A23" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:7">
+      <x:c r="A24" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:7">
+      <x:c r="A25" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:7">
+      <x:c r="A26" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Hand_edited_log/1/StudentsSolution.xlsx
+++ b/Hand_edited_log/1/StudentsSolution.xlsx
@@ -43,58 +43,52 @@
     <x:t>AnhDThe187386</x:t>
   </x:si>
   <x:si>
+    <x:t>Not Run</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>anlpvhe187047</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cuongnvhe181200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ducnthe180869</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungdvhe181404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungtdhe186461</x:t>
+  </x:si>
+  <x:si>
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 12:59:03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 13:01:01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>anlpvhe187047</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 13:01:17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cuongnvhe181200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 13:01:07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ducnthe180869</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Failed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 12:59:32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dungdvhe181404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dungtdhe186461</x:t>
+    <x:t>07-12-2025 14:45:11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 14:46:44</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>
@@ -103,19 +97,10 @@
     <x:t>duongnthe186310</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 13:01:40</x:t>
-  </x:si>
-  <x:si>
     <x:t>8</x:t>
   </x:si>
   <x:si>
     <x:t>DuyCNHE187327</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Not Run</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
   </x:si>
   <x:si>
     <x:t>9</x:t>
@@ -244,7 +229,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -259,11 +244,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -286,7 +266,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="4">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -296,11 +276,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -310,10 +287,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -647,578 +620,578 @@
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7">
-      <x:c r="A2" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
+      <x:c r="A2" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C2" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="s">
+      <x:c r="C2" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:7">
+      <x:c r="A3" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
-      <x:c r="A3" s="2" t="s">
+      <x:c r="B3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="s">
+      <x:c r="C3" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F3" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G3" s="2" t="s">
+      <x:c r="B4" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="2" t="s">
+      <x:c r="C4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:7">
+      <x:c r="A5" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B4" s="2" t="s">
+      <x:c r="B5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C4" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E4" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G4" s="2" t="s">
+      <x:c r="C5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:7">
+      <x:c r="A6" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" spans="1:7">
-      <x:c r="A5" s="3" t="s">
+      <x:c r="B6" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B5" s="3" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C5" s="3" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E5" s="3" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F5" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G5" s="3" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:7">
-      <x:c r="A6" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B6" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C6" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E6" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F6" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G6" s="2" t="s">
-        <x:v>15</x:v>
+      <x:c r="C6" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B7" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E7" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F7" s="2" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G7" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:7">
+      <x:c r="A8" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B7" s="2" t="s">
+      <x:c r="B8" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C7" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E7" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F7" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G7" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:7">
-      <x:c r="A8" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B8" s="2" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E8" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F8" s="2" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G8" s="2" t="s">
-        <x:v>29</x:v>
+      <x:c r="C8" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Hand_edited_log/1/StudentsSolution.xlsx
+++ b/Hand_edited_log/1/StudentsSolution.xlsx
@@ -43,70 +43,91 @@
     <x:t>AnhDThe187386</x:t>
   </x:si>
   <x:si>
+    <x:t>Success</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 15:08:20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 15:10:34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>anlpvhe187047</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 15:10:49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cuongnvhe181200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 15:10:40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ducnthe180869</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Failed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 15:09:08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungdvhe181404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 15:10:47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungtdhe186461</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duongnthe186310</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 15:10:51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DuyCNHE187327</x:t>
+  </x:si>
+  <x:si>
     <x:t>Not Run</x:t>
   </x:si>
   <x:si>
-    <x:t>0</x:t>
-  </x:si>
-  <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>anlpvhe187047</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cuongnvhe181200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ducnthe180869</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dungdvhe181404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dungtdhe186461</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Success</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 14:45:11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 14:46:44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duongnthe186310</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DuyCNHE187327</x:t>
-  </x:si>
-  <x:si>
     <x:t>9</x:t>
   </x:si>
   <x:si>
     <x:t>duyldhe176352</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 15:10:50</x:t>
   </x:si>
   <x:si>
     <x:t>10</x:t>
@@ -229,7 +250,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -244,6 +265,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -266,7 +292,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -276,8 +302,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -287,6 +316,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -620,578 +653,578 @@
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7">
-      <x:c r="A2" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
+      <x:c r="A2" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="C2" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
+      <x:c r="E2" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
+      <x:c r="F2" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s">
+      <x:c r="G2" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:7">
+      <x:c r="A3" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F3" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
-      <x:c r="A3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="G3" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D4" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="E4" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
+      <x:c r="F4" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
+      <x:c r="G4" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:7">
+      <x:c r="A5" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D5" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E5" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F5" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="G5" s="3" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:7">
+      <x:c r="A6" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C6" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D6" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
+      <x:c r="E6" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F6" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:7">
-      <x:c r="A5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:7">
-      <x:c r="A6" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>11</x:v>
+      <x:c r="G6" s="2" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E7" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F7" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G7" s="2" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F7" s="2" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G7" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
-      <x:c r="A8" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
+      <x:c r="A8" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B8" s="2" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
+      <x:c r="E8" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F8" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>11</x:v>
+      <x:c r="G8" s="2" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:7">
+      <x:c r="A10" s="2" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B10" s="2" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E10" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F10" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" spans="1:7">
-      <x:c r="A10" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
+      <x:c r="G10" s="2" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:7">
+      <x:c r="A11" s="2" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B11" s="2" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E11" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F11" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G11" s="2" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:7">
-      <x:c r="A11" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Hand_edited_log/1/StudentsSolution.xlsx
+++ b/Hand_edited_log/1/StudentsSolution.xlsx
@@ -43,61 +43,52 @@
     <x:t>AnhDThe187386</x:t>
   </x:si>
   <x:si>
+    <x:t>Not Run</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>anlpvhe187047</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cuongnvhe181200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ducnthe180869</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungdvhe181404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungtdhe186461</x:t>
+  </x:si>
+  <x:si>
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 15:08:20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 15:10:34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>anlpvhe187047</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 15:10:49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cuongnvhe181200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 15:10:40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ducnthe180869</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Failed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 15:09:08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dungdvhe181404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 15:10:47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dungtdhe186461</x:t>
+    <x:t>07-12-2025 16:29:56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 16:31:28</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>
@@ -106,28 +97,16 @@
     <x:t>duongnthe186310</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 15:10:51</x:t>
-  </x:si>
-  <x:si>
     <x:t>8</x:t>
   </x:si>
   <x:si>
     <x:t>DuyCNHE187327</x:t>
   </x:si>
   <x:si>
-    <x:t>Not Run</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
     <x:t>9</x:t>
   </x:si>
   <x:si>
     <x:t>duyldhe176352</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 15:10:50</x:t>
   </x:si>
   <x:si>
     <x:t>10</x:t>
@@ -250,7 +229,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -265,11 +244,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -292,7 +266,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="4">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -302,11 +276,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -316,10 +287,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -653,578 +620,578 @@
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7">
-      <x:c r="A2" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
+      <x:c r="A2" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C2" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="s">
+      <x:c r="C2" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:7">
+      <x:c r="A3" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
-      <x:c r="A3" s="2" t="s">
+      <x:c r="B3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="s">
+      <x:c r="C3" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F3" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G3" s="2" t="s">
+      <x:c r="B4" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="2" t="s">
+      <x:c r="C4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:7">
+      <x:c r="A5" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B4" s="2" t="s">
+      <x:c r="B5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C4" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E4" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G4" s="2" t="s">
+      <x:c r="C5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:7">
+      <x:c r="A6" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" spans="1:7">
-      <x:c r="A5" s="3" t="s">
+      <x:c r="B6" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B5" s="3" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C5" s="3" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E5" s="3" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F5" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G5" s="3" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:7">
-      <x:c r="A6" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B6" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C6" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E6" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F6" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G6" s="2" t="s">
-        <x:v>25</x:v>
+      <x:c r="C6" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B7" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E7" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F7" s="2" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G7" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:7">
+      <x:c r="A8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B7" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C7" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E7" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F7" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G7" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:7">
-      <x:c r="A8" s="2" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B8" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C8" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E8" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F8" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G8" s="2" t="s">
-        <x:v>30</x:v>
+      <x:c r="C8" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:7">
+      <x:c r="A10" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:7">
+      <x:c r="A11" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
+      <x:c r="B11" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:7">
-      <x:c r="A10" s="2" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B10" s="2" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C10" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E10" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F10" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G10" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:7">
-      <x:c r="A11" s="2" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B11" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C11" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E11" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F11" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G11" s="2" t="s">
-        <x:v>30</x:v>
+      <x:c r="C11" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Hand_edited_log/1/StudentsSolution.xlsx
+++ b/Hand_edited_log/1/StudentsSolution.xlsx
@@ -85,10 +85,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 16:29:56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 16:31:28</x:t>
+    <x:t>07-12-2025 16:41:43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 16:43:31</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>

--- a/Hand_edited_log/1/StudentsSolution.xlsx
+++ b/Hand_edited_log/1/StudentsSolution.xlsx
@@ -85,10 +85,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 16:41:43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 16:43:31</x:t>
+    <x:t>07-12-2025 17:26:23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 17:27:58</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>

--- a/Hand_edited_log/1/StudentsSolution.xlsx
+++ b/Hand_edited_log/1/StudentsSolution.xlsx
@@ -85,10 +85,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 17:26:23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 17:27:58</x:t>
+    <x:t>07-12-2025 17:45:16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 17:46:52</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>

--- a/Hand_edited_log/1/StudentsSolution.xlsx
+++ b/Hand_edited_log/1/StudentsSolution.xlsx
@@ -85,10 +85,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 17:45:16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 17:46:52</x:t>
+    <x:t>07-12-2025 18:01:25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 18:03:26</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>

--- a/Hand_edited_log/1/StudentsSolution.xlsx
+++ b/Hand_edited_log/1/StudentsSolution.xlsx
@@ -85,10 +85,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 18:01:25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 18:03:26</x:t>
+    <x:t>07-12-2025 18:40:45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 18:42:18</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>

--- a/Hand_edited_log/1/StudentsSolution.xlsx
+++ b/Hand_edited_log/1/StudentsSolution.xlsx
@@ -85,10 +85,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 18:40:45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 18:42:18</x:t>
+    <x:t>07-12-2025 19:21:44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07-12-2025 19:23:14</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>

--- a/Hand_edited_log/1/StudentsSolution.xlsx
+++ b/Hand_edited_log/1/StudentsSolution.xlsx
@@ -85,10 +85,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>07-12-2025 19:21:44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07-12-2025 19:23:14</x:t>
+    <x:t>08-12-2025 01:07:20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 01:08:59</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>

--- a/Hand_edited_log/1/StudentsSolution.xlsx
+++ b/Hand_edited_log/1/StudentsSolution.xlsx
@@ -85,10 +85,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 01:07:20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08-12-2025 01:08:59</x:t>
+    <x:t>08-12-2025 01:29:12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 01:30:44</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>
